--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:10</t>
+    <t xml:space="preserve">2026-10-05 10:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -556,7 +556,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1137302.12</v>
+        <v>1137302.13</v>
       </c>
     </row>
     <row r="6">
